--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/CALIFORNIA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/CALIFORNIA_2014.xlsx
@@ -1021,7 +1021,7 @@
         <v>30</v>
       </c>
       <c r="D37">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="38">
@@ -2461,7 +2461,7 @@
         <v>294</v>
       </c>
       <c r="D117">
-        <v>0.00095746759591</v>
+        <v>0.0009574675959100002</v>
       </c>
     </row>
     <row r="118">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C198">
@@ -7771,7 +7771,7 @@
         <v>30</v>
       </c>
       <c r="D412">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="413">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C417">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C427">
@@ -8059,7 +8059,7 @@
         <v>294</v>
       </c>
       <c r="D428">
-        <v>0.00095746759591</v>
+        <v>0.0009574675959100002</v>
       </c>
     </row>
     <row r="429">
@@ -9283,7 +9283,7 @@
         <v>283</v>
       </c>
       <c r="D496">
-        <v>0.000921643978376</v>
+        <v>0.0009216439783760002</v>
       </c>
     </row>
     <row r="497">
@@ -9607,7 +9607,7 @@
         <v>281</v>
       </c>
       <c r="D514">
-        <v>0.000915130593369</v>
+        <v>0.0009151305933690002</v>
       </c>
     </row>
     <row r="515">
@@ -9805,7 +9805,7 @@
         <v>294</v>
       </c>
       <c r="D525">
-        <v>0.00095746759591</v>
+        <v>0.0009574675959100002</v>
       </c>
     </row>
     <row r="526">
@@ -10579,7 +10579,7 @@
         <v>30</v>
       </c>
       <c r="D568">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="569">
@@ -11803,7 +11803,7 @@
         <v>30</v>
       </c>
       <c r="D636">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="637">
@@ -12685,7 +12685,7 @@
         <v>299</v>
       </c>
       <c r="D685">
-        <v>0.000973751058425</v>
+        <v>0.0009737510584250002</v>
       </c>
     </row>
     <row r="686">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C921">
@@ -20047,7 +20047,7 @@
         <v>30</v>
       </c>
       <c r="D1094">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1095">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1149">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1150">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1249">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1250">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1263">
@@ -23863,7 +23863,7 @@
         <v>30</v>
       </c>
       <c r="D1306">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1307">
@@ -24817,7 +24817,7 @@
         <v>30</v>
       </c>
       <c r="D1359">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1360">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1438">
@@ -28471,7 +28471,7 @@
         <v>30</v>
       </c>
       <c r="D1562">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1563">
@@ -29065,7 +29065,7 @@
         <v>30</v>
       </c>
       <c r="D1595">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1596">
@@ -32359,7 +32359,7 @@
         <v>30</v>
       </c>
       <c r="D1778">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1779">
@@ -33511,7 +33511,7 @@
         <v>30</v>
       </c>
       <c r="D1842">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1843">
@@ -34800,7 +34800,7 @@
       </c>
       <c r="B1914" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1914">
@@ -35545,7 +35545,7 @@
         <v>30</v>
       </c>
       <c r="D1955">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1956">
@@ -35689,7 +35689,7 @@
         <v>30</v>
       </c>
       <c r="D1963">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="1964">
@@ -35718,7 +35718,7 @@
       </c>
       <c r="B1965" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1965">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="B2152" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C2152">
@@ -39919,7 +39919,7 @@
         <v>30</v>
       </c>
       <c r="D2198">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="2199">
@@ -41143,7 +41143,7 @@
         <v>30</v>
       </c>
       <c r="D2266">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="2267">
@@ -41179,7 +41179,7 @@
         <v>30</v>
       </c>
       <c r="D2268">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="2269">
@@ -41323,7 +41323,7 @@
         <v>283</v>
       </c>
       <c r="D2276">
-        <v>0.000921643978376</v>
+        <v>0.0009216439783760002</v>
       </c>
     </row>
     <row r="2277">
@@ -41773,7 +41773,7 @@
         <v>30</v>
       </c>
       <c r="D2301">
-        <v>9.7700775093E-05</v>
+        <v>9.770077509300001E-05</v>
       </c>
     </row>
     <row r="2302">
